--- a/plantillas/consulta/Mesas_CSC.xlsx
+++ b/plantillas/consulta/Mesas_CSC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E89BBD6-CE02-4362-A7B5-9C9B9D9AC710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF0FDA8-BB71-4EA3-B16C-6905CC35A950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -148,7 +148,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -195,6 +195,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -524,7 +530,7 @@
       <c r="C2" s="15"/>
       <c r="D2" s="16"/>
     </row>
-    <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="14"/>
@@ -555,15 +561,18 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B8" s="5"/>
-      <c r="D8" s="9" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="17" t="s">
         <v>0</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="9"/>
+      <c r="E9" s="17" t="s">
         <v>1</v>
       </c>
     </row>
